--- a/EndResult/400m Medley.xlsx
+++ b/EndResult/400m Medley.xlsx
@@ -1775,12 +1775,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.30,43</t>
+          <t>5.30,45</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.06.2019</t>
+          <t>04.03.2016</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1810,12 +1810,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.30,45</t>
+          <t>5.30,43</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04.03.2016</t>
+          <t>30.06.2019</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/EndResult/400m Medley.xlsx
+++ b/EndResult/400m Medley.xlsx
@@ -1304,25 +1304,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sara Juul Wolfgang</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.10,61</t>
+          <t>5.04,16</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>579</v>
+        <v>617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.03.2016</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1339,25 +1339,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Sara Juul Wolfgang</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.15,46</t>
+          <t>5.10,61</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.01.2015</t>
+          <t>13.03.2016</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1374,20 +1374,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.19,28</t>
+          <t>5.15,46</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>18.01.2015</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1409,25 +1409,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.22,37</t>
+          <t>5.19,28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05.06.2010</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1444,25 +1444,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tove Fludal Haugan</t>
+          <t>Irja Gravdahl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.25,96</t>
+          <t>5.22,37</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.04.2005</t>
+          <t>05.06.2010</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1479,25 +1479,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gudrun Berg Ildstad</t>
+          <t>Tove Fludal Haugan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.26,40</t>
+          <t>5.25,96</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23.01.2011</t>
+          <t>16.04.2005</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1514,20 +1514,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Stine Tveit</t>
+          <t>Gudrun Berg Ildstad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.28,00</t>
+          <t>5.26,40</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.10.2009</t>
+          <t>23.01.2011</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1549,25 +1549,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Christiana Bjørkli</t>
+          <t>Stine Tveit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.31,63</t>
+          <t>5.28,00</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>11.10.2009</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1584,25 +1584,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maja Graczyk</t>
+          <t>Christiana Bjørkli</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.31,78</t>
+          <t>5.31,63</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
